--- a/data/saeop/사회참여권익증진.xlsx
+++ b/data/saeop/사회참여권익증진.xlsx
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J38"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1121,7 +1121,7 @@
         <v>문의</v>
       </c>
       <c r="G20" t="str">
-        <v>복지사업팀 033-747-0516</v>
+        <v>지역복지팀 033-747-0516</v>
       </c>
       <c r="H20" t="str">
         <v>phone</v>
@@ -1165,7 +1165,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" xml:space="preserve">
       <c r="A22" t="str">
         <v>O</v>
       </c>
@@ -1184,8 +1184,9 @@
       <c r="F22" t="str">
         <v>노인권익증진교육</v>
       </c>
-      <c r="G22" t="str">
-        <v>노인학대예방교육</v>
+      <c r="G22" t="str" xml:space="preserve">
+        <v xml:space="preserve">소비자피해예방교육
+* 한국소비자단체협의회 연계</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -1197,7 +1198,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" xml:space="preserve">
       <c r="A23" t="str">
         <v>O</v>
       </c>
@@ -1216,8 +1217,9 @@
       <c r="F23" t="str">
         <v>노인권익증진교육</v>
       </c>
-      <c r="G23" t="str">
-        <v>노인소비자피해예방교육</v>
+      <c r="G23" t="str" xml:space="preserve">
+        <v xml:space="preserve">양성평등교육
+* 원주여성민우회 연계</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -1229,7 +1231,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" xml:space="preserve">
       <c r="A24" t="str">
         <v>O</v>
       </c>
@@ -1248,8 +1250,9 @@
       <c r="F24" t="str">
         <v>노인권익증진교육</v>
       </c>
-      <c r="G24" t="str">
-        <v>양성평등교육</v>
+      <c r="G24" t="str" xml:space="preserve">
+        <v xml:space="preserve">노인인권교육 및 이동상담소
+* 강원남부노인보호전문기관 연계</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1261,7 +1264,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" xml:space="preserve">
       <c r="A25" t="str">
         <v>O</v>
       </c>
@@ -1280,8 +1283,9 @@
       <c r="F25" t="str">
         <v>노인권익증진교육</v>
       </c>
-      <c r="G25" t="str">
-        <v>성교육</v>
+      <c r="G25" t="str" xml:space="preserve">
+        <v xml:space="preserve">어르신 식생활 교육
+* 식생활교육강원네트워크 연계</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -1293,7 +1297,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" xml:space="preserve">
       <c r="A26" t="str">
         <v>O</v>
       </c>
@@ -1312,8 +1316,9 @@
       <c r="F26" t="str">
         <v>노인권익증진교육</v>
       </c>
-      <c r="G26" t="str">
-        <v>노인인권교육</v>
+      <c r="G26" t="str" xml:space="preserve">
+        <v xml:space="preserve">어르신 건강 교실 교육
+* 우유자조금관리위원회 연계</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -1325,7 +1330,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" xml:space="preserve">
       <c r="A27" t="str">
         <v>O</v>
       </c>
@@ -1344,8 +1349,10 @@
       <c r="F27" t="str">
         <v>노인인식개선사업</v>
       </c>
-      <c r="G27" t="str">
-        <v>지역사회 주민 대상 노인인식개선 캠페인 등 진행</v>
+      <c r="G27" t="str" xml:space="preserve">
+        <v xml:space="preserve">지역사회 주민 대상 노인인식개선 캠페인 등 진행
+- 노인권익증진캠페인
+- 노인학대예방캠페인</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1368,16 +1375,16 @@
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>지역주민 공청회</v>
+        <v>노인권익증진</v>
       </c>
       <c r="E28" t="str">
-        <v>설명</v>
+        <v>사진</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>소비자피해예방교육</v>
       </c>
       <c r="G28" t="str">
-        <v>지역주민의 목소리를 직접 들으며 함께 지역 내 현안·사회문제 해결을 도모하는 소통의 장을 마련합니다.</v>
+        <v>KakaoTalk_20260829_095557363_02.jpg</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1400,19 +1407,19 @@
         <v/>
       </c>
       <c r="D29" t="str">
-        <v>지역주민 공청회</v>
+        <v>노인권익증진</v>
       </c>
       <c r="E29" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F29" t="str">
-        <v>이용 대상</v>
+        <v>노인인권교육</v>
       </c>
       <c r="G29" t="str">
-        <v>함께 소통하고 싶은 지역주민</v>
+        <v>KakaoTalk_20260916_151542383_08.jpg</v>
       </c>
       <c r="H29" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1432,19 +1439,19 @@
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>지역주민 공청회</v>
+        <v>노인권익증진</v>
       </c>
       <c r="E30" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F30" t="str">
-        <v>일정</v>
+        <v>어르신 건강 교실 교육</v>
       </c>
       <c r="G30" t="str">
-        <v>상·하반기 진행</v>
+        <v>KakaoTalk_20260829_094758193_04.jpg</v>
       </c>
       <c r="H30" t="str">
-        <v>clock</v>
+        <v/>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1464,22 +1471,22 @@
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>지역주민 공청회</v>
+        <v>노인권익증진</v>
       </c>
       <c r="E31" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F31" t="str">
-        <v>문의</v>
+        <v>어르신 식생활 교육</v>
       </c>
       <c r="G31" t="str">
-        <v>복지사업팀 033-747-0516</v>
+        <v>KakaoTalk_20260701_122721226.jpg</v>
       </c>
       <c r="H31" t="str">
-        <v>phone</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -1499,13 +1506,13 @@
         <v>지역주민 공청회</v>
       </c>
       <c r="E32" t="str">
-        <v>내용제목</v>
+        <v>설명</v>
       </c>
       <c r="F32" t="str">
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>사업 내용</v>
+        <v>지역주민의 목소리를 직접 들으며 함께 지역 내 현안·사회문제 해결을 도모하는 소통의 장을 마련합니다.</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -1531,16 +1538,16 @@
         <v>지역주민 공청회</v>
       </c>
       <c r="E33" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F33" t="str">
-        <v>지역주민 공청회</v>
+        <v>이용 대상</v>
       </c>
       <c r="G33" t="str">
-        <v>지역주민 공청회를 진행하여 지역 내 욕구 확인</v>
+        <v>함께 소통하고 싶은 지역주민</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>user</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1563,27 +1570,155 @@
         <v>지역주민 공청회</v>
       </c>
       <c r="E34" t="str">
+        <v>정보</v>
+      </c>
+      <c r="F34" t="str">
+        <v>일정</v>
+      </c>
+      <c r="G34" t="str">
+        <v>상·하반기 진행</v>
+      </c>
+      <c r="H34" t="str">
+        <v>clock</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>O</v>
+      </c>
+      <c r="B35" t="str">
+        <v>chamyeo</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v>지역주민 공청회</v>
+      </c>
+      <c r="E35" t="str">
+        <v>정보</v>
+      </c>
+      <c r="F35" t="str">
+        <v>문의</v>
+      </c>
+      <c r="G35" t="str">
+        <v>복지사업팀 033-747-0516</v>
+      </c>
+      <c r="H35" t="str">
+        <v>phone</v>
+      </c>
+      <c r="I35" t="str">
+        <v>033-747-0516</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>O</v>
+      </c>
+      <c r="B36" t="str">
+        <v>chamyeo</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v>지역주민 공청회</v>
+      </c>
+      <c r="E36" t="str">
+        <v>내용제목</v>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v>사업 내용</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>O</v>
+      </c>
+      <c r="B37" t="str">
+        <v>chamyeo</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v>지역주민 공청회</v>
+      </c>
+      <c r="E37" t="str">
         <v>내용</v>
       </c>
-      <c r="F34" t="str">
+      <c r="F37" t="str">
         <v>지역주민 공청회</v>
       </c>
-      <c r="G34" t="str">
+      <c r="G37" t="str">
+        <v>지역주민 공청회를 진행하여 지역 내 욕구 확인</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>O</v>
+      </c>
+      <c r="B38" t="str">
+        <v>chamyeo</v>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v>지역주민 공청회</v>
+      </c>
+      <c r="E38" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F38" t="str">
+        <v>지역주민 공청회</v>
+      </c>
+      <c r="G38" t="str">
         <v>지역 내 노인복지관의 올바른 운영을 위한 방향성 논의</v>
       </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
-      <c r="I34" t="str">
-        <v/>
-      </c>
-      <c r="J34" t="str">
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J38"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/사회참여권익증진.xlsx
+++ b/data/saeop/사회참여권익증진.xlsx
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -894,10 +894,10 @@
         <v>내용</v>
       </c>
       <c r="F13" t="str">
-        <v>선배시민 활동</v>
+        <v>세대공감 더-이음 활동</v>
       </c>
       <c r="G13" t="str">
-        <v>선배시민으로서 지역사회와 선배 후배세대를 위한 정책 제안 활동과 선배시민정책대회 운영, 노인권익캠페인 진행</v>
+        <v>어르신과 아이들, 1 3세대가 함께하는 세대 화합 봉사활동</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -923,13 +923,13 @@
         <v>북원보듬 선배시민봉사단</v>
       </c>
       <c r="E14" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F14" t="str">
-        <v>솔선봉사단</v>
+        <v>선배시민 활동</v>
       </c>
       <c r="G14" t="str">
-        <v>KakaoTalk_20260203_104534031_01.jpg</v>
+        <v>선배시민으로서 지역사회와 선배 후배세대를 위한 정책 제안 활동과 선배시민정책대회 운영, 노인권익캠페인 진행</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -958,10 +958,10 @@
         <v>사진</v>
       </c>
       <c r="F15" t="str">
-        <v>러브레드봉사단</v>
+        <v>솔선봉사단</v>
       </c>
       <c r="G15" t="str">
-        <v>KakaoTalk_20260311_144849685.jpg</v>
+        <v>KakaoTalk_20260203_104534031_01.jpg</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -990,10 +990,10 @@
         <v>사진</v>
       </c>
       <c r="F16" t="str">
-        <v>미소봉사단</v>
+        <v>러브레드봉사단</v>
       </c>
       <c r="G16" t="str">
-        <v>KakaoTalk_20260829_093748938_02.jpg</v>
+        <v>KakaoTalk_20260311_144849685.jpg</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1022,10 +1022,10 @@
         <v>사진</v>
       </c>
       <c r="F17" t="str">
-        <v>선배시민정책대회</v>
+        <v>미소봉사단</v>
       </c>
       <c r="G17" t="str">
-        <v>KakaoTalk_20261008_163859452_09.jpg</v>
+        <v>KakaoTalk_20260829_093748938_02.jpg</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -1048,16 +1048,16 @@
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>노인권익증진</v>
+        <v>북원보듬 선배시민봉사단</v>
       </c>
       <c r="E18" t="str">
-        <v>설명</v>
+        <v>사진</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>세대공감 더-이음 활동</v>
       </c>
       <c r="G18" t="str">
-        <v>노인학대예방·인권 교육과 인식개선 캠페인을 통해 어르신의 권익을 보호하고 증진합니다.</v>
+        <v>KakaoTalk_20260609_123859791.jpg</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -1083,16 +1083,16 @@
         <v>노인권익증진</v>
       </c>
       <c r="E19" t="str">
-        <v>정보</v>
+        <v>설명</v>
       </c>
       <c r="F19" t="str">
-        <v>이용 대상</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v>노인권익증진 교육 참여 희망 복지관 이용자</v>
+        <v>노인학대예방·인권 교육과 인식개선 캠페인을 통해 어르신의 권익을 보호하고 증진합니다.</v>
       </c>
       <c r="H19" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1118,16 +1118,16 @@
         <v>정보</v>
       </c>
       <c r="F20" t="str">
-        <v>문의</v>
+        <v>이용 대상</v>
       </c>
       <c r="G20" t="str">
-        <v>지역복지팀 033-747-0516</v>
+        <v>노인권익증진 교육 참여 희망 복지관 이용자</v>
       </c>
       <c r="H20" t="str">
-        <v>phone</v>
+        <v>user</v>
       </c>
       <c r="I20" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1147,25 +1147,25 @@
         <v>노인권익증진</v>
       </c>
       <c r="E21" t="str">
-        <v>내용제목</v>
+        <v>정보</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>문의</v>
       </c>
       <c r="G21" t="str">
-        <v>사업 내용</v>
+        <v>지역복지팀 033-747-0516</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J21" t="str">
         <v/>
       </c>
     </row>
-    <row r="22" xml:space="preserve">
+    <row r="22">
       <c r="A22" t="str">
         <v>O</v>
       </c>
@@ -1179,213 +1179,213 @@
         <v>노인권익증진</v>
       </c>
       <c r="E22" t="str">
+        <v>내용제목</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>사업 내용</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>O</v>
+      </c>
+      <c r="B23" t="str">
+        <v>chamyeo</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>노인권익증진</v>
+      </c>
+      <c r="E23" t="str">
         <v>내용</v>
       </c>
-      <c r="F22" t="str">
+      <c r="F23" t="str">
         <v>노인권익증진교육</v>
       </c>
-      <c r="G22" t="str" xml:space="preserve">
+      <c r="G23" t="str" xml:space="preserve">
         <v xml:space="preserve">소비자피해예방교육
 * 한국소비자단체협의회 연계</v>
       </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
-      <c r="A23" t="str">
-        <v>O</v>
-      </c>
-      <c r="B23" t="str">
-        <v>chamyeo</v>
-      </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>O</v>
+      </c>
+      <c r="B24" t="str">
+        <v>chamyeo</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
         <v>노인권익증진</v>
       </c>
-      <c r="E23" t="str">
+      <c r="E24" t="str">
         <v>내용</v>
       </c>
-      <c r="F23" t="str">
+      <c r="F24" t="str">
         <v>노인권익증진교육</v>
       </c>
-      <c r="G23" t="str" xml:space="preserve">
+      <c r="G24" t="str" xml:space="preserve">
         <v xml:space="preserve">양성평등교육
 * 원주여성민우회 연계</v>
       </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24" xml:space="preserve">
-      <c r="A24" t="str">
-        <v>O</v>
-      </c>
-      <c r="B24" t="str">
-        <v>chamyeo</v>
-      </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>O</v>
+      </c>
+      <c r="B25" t="str">
+        <v>chamyeo</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
         <v>노인권익증진</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E25" t="str">
         <v>내용</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F25" t="str">
         <v>노인권익증진교육</v>
       </c>
-      <c r="G24" t="str" xml:space="preserve">
+      <c r="G25" t="str" xml:space="preserve">
         <v xml:space="preserve">노인인권교육 및 이동상담소
 * 강원남부노인보호전문기관 연계</v>
       </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25" t="str">
-        <v>O</v>
-      </c>
-      <c r="B25" t="str">
-        <v>chamyeo</v>
-      </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>O</v>
+      </c>
+      <c r="B26" t="str">
+        <v>chamyeo</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
         <v>노인권익증진</v>
       </c>
-      <c r="E25" t="str">
+      <c r="E26" t="str">
         <v>내용</v>
       </c>
-      <c r="F25" t="str">
+      <c r="F26" t="str">
         <v>노인권익증진교육</v>
       </c>
-      <c r="G25" t="str" xml:space="preserve">
+      <c r="G26" t="str" xml:space="preserve">
         <v xml:space="preserve">어르신 식생활 교육
 * 식생활교육강원네트워크 연계</v>
       </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26" xml:space="preserve">
-      <c r="A26" t="str">
-        <v>O</v>
-      </c>
-      <c r="B26" t="str">
-        <v>chamyeo</v>
-      </c>
-      <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="D26" t="str">
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>O</v>
+      </c>
+      <c r="B27" t="str">
+        <v>chamyeo</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
         <v>노인권익증진</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E27" t="str">
         <v>내용</v>
       </c>
-      <c r="F26" t="str">
+      <c r="F27" t="str">
         <v>노인권익증진교육</v>
       </c>
-      <c r="G26" t="str" xml:space="preserve">
+      <c r="G27" t="str" xml:space="preserve">
         <v xml:space="preserve">어르신 건강 교실 교육
 * 우유자조금관리위원회 연계</v>
       </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27" t="str">
-        <v>O</v>
-      </c>
-      <c r="B27" t="str">
-        <v>chamyeo</v>
-      </c>
-      <c r="C27" t="str">
-        <v/>
-      </c>
-      <c r="D27" t="str">
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>O</v>
+      </c>
+      <c r="B28" t="str">
+        <v>chamyeo</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
         <v>노인권익증진</v>
       </c>
-      <c r="E27" t="str">
+      <c r="E28" t="str">
         <v>내용</v>
       </c>
-      <c r="F27" t="str">
+      <c r="F28" t="str">
         <v>노인인식개선사업</v>
       </c>
-      <c r="G27" t="str" xml:space="preserve">
+      <c r="G28" t="str" xml:space="preserve">
         <v xml:space="preserve">지역사회 주민 대상 노인인식개선 캠페인 등 진행
 - 노인권익증진캠페인
 - 노인학대예방캠페인</v>
       </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>O</v>
-      </c>
-      <c r="B28" t="str">
-        <v>chamyeo</v>
-      </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <v>노인권익증진</v>
-      </c>
-      <c r="E28" t="str">
-        <v>사진</v>
-      </c>
-      <c r="F28" t="str">
-        <v>소비자피해예방교육</v>
-      </c>
-      <c r="G28" t="str">
-        <v>KakaoTalk_20260829_095557363_02.jpg</v>
-      </c>
       <c r="H28" t="str">
         <v/>
       </c>
@@ -1413,10 +1413,10 @@
         <v>사진</v>
       </c>
       <c r="F29" t="str">
-        <v>노인인권교육</v>
+        <v>소비자피해예방교육</v>
       </c>
       <c r="G29" t="str">
-        <v>KakaoTalk_20260916_151542383_08.jpg</v>
+        <v>KakaoTalk_20260829_095557363_02.jpg</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -1445,10 +1445,10 @@
         <v>사진</v>
       </c>
       <c r="F30" t="str">
-        <v>어르신 건강 교실 교육</v>
+        <v>노인인권교육</v>
       </c>
       <c r="G30" t="str">
-        <v>KakaoTalk_20260829_094758193_04.jpg</v>
+        <v>KakaoTalk_20260916_151542383_08.jpg</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -1477,10 +1477,10 @@
         <v>사진</v>
       </c>
       <c r="F31" t="str">
-        <v>어르신 식생활 교육</v>
+        <v>어르신 건강 교실 교육</v>
       </c>
       <c r="G31" t="str">
-        <v>KakaoTalk_20260701_122721226.jpg</v>
+        <v>KakaoTalk_20260829_094758193_04.jpg</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -1503,16 +1503,16 @@
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>지역주민 공청회</v>
+        <v>노인권익증진</v>
       </c>
       <c r="E32" t="str">
-        <v>설명</v>
+        <v>사진</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>어르신 식생활 교육</v>
       </c>
       <c r="G32" t="str">
-        <v>지역주민의 목소리를 직접 들으며 함께 지역 내 현안·사회문제 해결을 도모하는 소통의 장을 마련합니다.</v>
+        <v>KakaoTalk_20260701_122721226.jpg</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -1538,16 +1538,16 @@
         <v>지역주민 공청회</v>
       </c>
       <c r="E33" t="str">
-        <v>정보</v>
+        <v>설명</v>
       </c>
       <c r="F33" t="str">
-        <v>이용 대상</v>
+        <v/>
       </c>
       <c r="G33" t="str">
-        <v>함께 소통하고 싶은 지역주민</v>
+        <v>지역주민의 목소리를 직접 들으며 함께 지역 내 현안·사회문제 해결을 도모하는 소통의 장을 마련합니다.</v>
       </c>
       <c r="H33" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1573,13 +1573,13 @@
         <v>정보</v>
       </c>
       <c r="F34" t="str">
-        <v>일정</v>
+        <v>이용 대상</v>
       </c>
       <c r="G34" t="str">
-        <v>상·하반기 진행</v>
+        <v>함께 소통하고 싶은 지역주민</v>
       </c>
       <c r="H34" t="str">
-        <v>clock</v>
+        <v>user</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1605,16 +1605,16 @@
         <v>정보</v>
       </c>
       <c r="F35" t="str">
-        <v>문의</v>
+        <v>일정</v>
       </c>
       <c r="G35" t="str">
-        <v>복지사업팀 033-747-0516</v>
+        <v>상·하반기 진행</v>
       </c>
       <c r="H35" t="str">
-        <v>phone</v>
+        <v>clock</v>
       </c>
       <c r="I35" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -1634,19 +1634,19 @@
         <v>지역주민 공청회</v>
       </c>
       <c r="E36" t="str">
-        <v>내용제목</v>
+        <v>정보</v>
       </c>
       <c r="F36" t="str">
-        <v/>
+        <v>문의</v>
       </c>
       <c r="G36" t="str">
-        <v>사업 내용</v>
+        <v>복지사업팀 033-747-0516</v>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -1666,13 +1666,13 @@
         <v>지역주민 공청회</v>
       </c>
       <c r="E37" t="str">
-        <v>내용</v>
+        <v>내용제목</v>
       </c>
       <c r="F37" t="str">
-        <v>지역주민 공청회</v>
+        <v/>
       </c>
       <c r="G37" t="str">
-        <v>지역주민 공청회를 진행하여 지역 내 욕구 확인</v>
+        <v>사업 내용</v>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -1704,21 +1704,53 @@
         <v>지역주민 공청회</v>
       </c>
       <c r="G38" t="str">
+        <v>지역주민 공청회를 진행하여 지역 내 욕구 확인</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>O</v>
+      </c>
+      <c r="B39" t="str">
+        <v>chamyeo</v>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v>지역주민 공청회</v>
+      </c>
+      <c r="E39" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F39" t="str">
+        <v>지역주민 공청회</v>
+      </c>
+      <c r="G39" t="str">
         <v>지역 내 노인복지관의 올바른 운영을 위한 방향성 논의</v>
       </c>
-      <c r="H38" t="str">
-        <v/>
-      </c>
-      <c r="I38" t="str">
-        <v/>
-      </c>
-      <c r="J38" t="str">
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J39"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/사회참여권익증진.xlsx
+++ b/data/saeop/사회참여권익증진.xlsx
@@ -897,7 +897,7 @@
         <v>세대공감 더-이음 활동</v>
       </c>
       <c r="G13" t="str">
-        <v>어르신과 아이들, 1 3세대가 함께하는 세대 화합 봉사활동</v>
+        <v>어르신과 아이들, 1 3세대가 함께하는 세대 화합 봉사활동    * 건강보험심사평가원 어린이집 연계</v>
       </c>
       <c r="H13" t="str">
         <v/>
